--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4923-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4923-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8986283-C371-42CA-98B3-0ED6E48B5872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C557D0AB-230E-43ED-8C2C-71491E5CA04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9588D184-4DC9-4050-A580-1CD541F12E18}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{ED4F528D-3F5E-4881-B4AC-22F578DC1CED}"/>
   </bookViews>
   <sheets>
     <sheet name="4923-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1499,30 +1499,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD690C25-138C-41EE-825D-B7161608C9B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7E7AB0-2307-4553-A607-11E9F2F6C083}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1592,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2023</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>2022</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="43"/>
       <c r="C10" s="19" t="s">
@@ -2102,7 +2102,7 @@
       <c r="W10" s="49"/>
       <c r="X10" s="45"/>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2021</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2020</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2019</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2018</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2017</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2016</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2015</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2014</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2013</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2012</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2011</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2010</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2009</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38" t="s">
         <v>43</v>
       </c>
